--- a/backend/data/Daywise MW Report.xlsx
+++ b/backend/data/Daywise MW Report.xlsx
@@ -154,7 +154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K656"/>
+  <dimension ref="A1:K713"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="13" customWidth="1"/>
@@ -896,7 +896,7 @@
         <v>0.026840</v>
       </c>
       <c r="I21" s="4">
-        <v>0.305840</v>
+        <v>0.305730</v>
       </c>
       <c r="J21" s="4">
         <v>0.009190</v>
@@ -1295,13 +1295,13 @@
         <v>45602</v>
       </c>
       <c r="B33" s="3">
-        <v>136920.000</v>
+        <v>135480.000</v>
       </c>
       <c r="C33" s="3">
         <v>1680.000</v>
       </c>
       <c r="D33" s="3">
-        <v>15240.000</v>
+        <v>16680.000</v>
       </c>
       <c r="E33" s="3">
         <v>0.000</v>
@@ -1310,13 +1310,13 @@
         <v>153840.000</v>
       </c>
       <c r="G33" s="4">
-        <v>1.033610</v>
+        <v>1.022960</v>
       </c>
       <c r="H33" s="4">
         <v>0.012640</v>
       </c>
       <c r="I33" s="4">
-        <v>0.113280</v>
+        <v>0.124070</v>
       </c>
       <c r="J33" s="4">
         <v>0.000000</v>
@@ -1470,10 +1470,10 @@
         <v>45607</v>
       </c>
       <c r="B38" s="3">
-        <v>141960.000</v>
+        <v>143640.000</v>
       </c>
       <c r="C38" s="3">
-        <v>25200.000</v>
+        <v>23520.000</v>
       </c>
       <c r="D38" s="3">
         <v>1680.000</v>
@@ -1485,10 +1485,10 @@
         <v>170400.000</v>
       </c>
       <c r="G38" s="4">
-        <v>1.071420</v>
+        <v>1.084280</v>
       </c>
       <c r="H38" s="4">
-        <v>0.186360</v>
+        <v>0.173890</v>
       </c>
       <c r="I38" s="4">
         <v>0.012420</v>
@@ -1590,7 +1590,7 @@
         <v>185880.000</v>
       </c>
       <c r="G41" s="4">
-        <v>1.169190</v>
+        <v>1.168990</v>
       </c>
       <c r="H41" s="4">
         <v>0.008350</v>
@@ -1695,7 +1695,7 @@
         <v>204360.000</v>
       </c>
       <c r="G44" s="4">
-        <v>1.160120</v>
+        <v>1.160250</v>
       </c>
       <c r="H44" s="4">
         <v>0.036970</v>
@@ -1707,7 +1707,7 @@
         <v>0.033170</v>
       </c>
       <c r="K44" s="3">
-        <v>1.537</v>
+        <v>1.538</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -1785,13 +1785,13 @@
         <v>45616</v>
       </c>
       <c r="B47" s="3">
-        <v>181200.000</v>
+        <v>182880.000</v>
       </c>
       <c r="C47" s="3">
         <v>1560.000</v>
       </c>
       <c r="D47" s="3">
-        <v>74880.000</v>
+        <v>73200.000</v>
       </c>
       <c r="E47" s="3">
         <v>0.000</v>
@@ -1800,13 +1800,13 @@
         <v>257640.000</v>
       </c>
       <c r="G47" s="4">
-        <v>1.370690</v>
+        <v>1.383330</v>
       </c>
       <c r="H47" s="4">
         <v>0.011740</v>
       </c>
       <c r="I47" s="4">
-        <v>0.561280</v>
+        <v>0.548860</v>
       </c>
       <c r="J47" s="4">
         <v>0.000000</v>
@@ -1820,13 +1820,13 @@
         <v>45617</v>
       </c>
       <c r="B48" s="3">
-        <v>193200.000</v>
+        <v>194880.000</v>
       </c>
       <c r="C48" s="3">
         <v>10080.000</v>
       </c>
       <c r="D48" s="3">
-        <v>55800.000</v>
+        <v>54120.000</v>
       </c>
       <c r="E48" s="3">
         <v>1680.000</v>
@@ -1835,13 +1835,13 @@
         <v>260760.000</v>
       </c>
       <c r="G48" s="4">
-        <v>1.460100</v>
+        <v>1.472730</v>
       </c>
       <c r="H48" s="4">
         <v>0.074720</v>
       </c>
       <c r="I48" s="4">
-        <v>0.417970</v>
+        <v>0.405270</v>
       </c>
       <c r="J48" s="4">
         <v>0.012250</v>
@@ -23100,34 +23100,2029 @@
         <v>46227</v>
       </c>
       <c r="B656" s="3">
-        <v>446740.000</v>
+        <v>716380.000</v>
       </c>
       <c r="C656" s="3">
+        <v>7280.000</v>
+      </c>
+      <c r="D656" s="3">
+        <v>54320.000</v>
+      </c>
+      <c r="E656" s="3">
+        <v>3360.000</v>
+      </c>
+      <c r="F656" s="3">
+        <v>781340.000</v>
+      </c>
+      <c r="G656" s="4">
+        <v>5.589170</v>
+      </c>
+      <c r="H656" s="4">
+        <v>0.056690</v>
+      </c>
+      <c r="I656" s="4">
+        <v>0.420150</v>
+      </c>
+      <c r="J656" s="4">
+        <v>0.026050</v>
+      </c>
+      <c r="K656" s="3">
+        <v>6.092</v>
+      </c>
+    </row>
+    <row r="657" spans="1:11">
+      <c r="A657" s="2">
+        <v>46228</v>
+      </c>
+      <c r="B657" s="3">
+        <v>707560.000</v>
+      </c>
+      <c r="C657" s="3">
+        <v>2940.000</v>
+      </c>
+      <c r="D657" s="3">
+        <v>58340.000</v>
+      </c>
+      <c r="E657" s="3">
+        <v>3640.000</v>
+      </c>
+      <c r="F657" s="3">
+        <v>772480.000</v>
+      </c>
+      <c r="G657" s="4">
+        <v>5.522540</v>
+      </c>
+      <c r="H657" s="4">
+        <v>0.022740</v>
+      </c>
+      <c r="I657" s="4">
+        <v>0.451590</v>
+      </c>
+      <c r="J657" s="4">
+        <v>0.028000</v>
+      </c>
+      <c r="K657" s="3">
+        <v>6.025</v>
+      </c>
+    </row>
+    <row r="658" spans="1:11">
+      <c r="A658" s="2">
+        <v>46229</v>
+      </c>
+      <c r="B658" s="3">
+        <v>692580.000</v>
+      </c>
+      <c r="C658" s="3">
+        <v>7280.000</v>
+      </c>
+      <c r="D658" s="3">
+        <v>55020.000</v>
+      </c>
+      <c r="E658" s="3">
+        <v>3920.000</v>
+      </c>
+      <c r="F658" s="3">
+        <v>758800.000</v>
+      </c>
+      <c r="G658" s="4">
+        <v>5.403700</v>
+      </c>
+      <c r="H658" s="4">
+        <v>0.056460</v>
+      </c>
+      <c r="I658" s="4">
+        <v>0.425820</v>
+      </c>
+      <c r="J658" s="4">
+        <v>0.029990</v>
+      </c>
+      <c r="K658" s="3">
+        <v>5.916</v>
+      </c>
+    </row>
+    <row r="659" spans="1:11">
+      <c r="A659" s="2">
+        <v>46230</v>
+      </c>
+      <c r="B659" s="3">
+        <v>698880.000</v>
+      </c>
+      <c r="C659" s="3">
+        <v>5320.000</v>
+      </c>
+      <c r="D659" s="3">
+        <v>59080.000</v>
+      </c>
+      <c r="E659" s="3">
+        <v>3920.000</v>
+      </c>
+      <c r="F659" s="3">
+        <v>767200.000</v>
+      </c>
+      <c r="G659" s="4">
+        <v>5.455030</v>
+      </c>
+      <c r="H659" s="4">
+        <v>0.041320</v>
+      </c>
+      <c r="I659" s="4">
+        <v>0.458220</v>
+      </c>
+      <c r="J659" s="4">
+        <v>0.029660</v>
+      </c>
+      <c r="K659" s="3">
+        <v>5.984</v>
+      </c>
+    </row>
+    <row r="660" spans="1:11">
+      <c r="A660" s="2">
+        <v>46231</v>
+      </c>
+      <c r="B660" s="3">
+        <v>680680.000</v>
+      </c>
+      <c r="C660" s="3">
+        <v>5320.000</v>
+      </c>
+      <c r="D660" s="3">
+        <v>68180.000</v>
+      </c>
+      <c r="E660" s="3">
+        <v>3500.000</v>
+      </c>
+      <c r="F660" s="3">
+        <v>757680.000</v>
+      </c>
+      <c r="G660" s="4">
+        <v>5.311450</v>
+      </c>
+      <c r="H660" s="4">
+        <v>0.041250</v>
+      </c>
+      <c r="I660" s="4">
+        <v>0.527710</v>
+      </c>
+      <c r="J660" s="4">
+        <v>0.026400</v>
+      </c>
+      <c r="K660" s="3">
+        <v>5.907</v>
+      </c>
+    </row>
+    <row r="661" spans="1:11">
+      <c r="A661" s="2">
+        <v>46232</v>
+      </c>
+      <c r="B661" s="3">
+        <v>685300.000</v>
+      </c>
+      <c r="C661" s="3">
+        <v>4900.000</v>
+      </c>
+      <c r="D661" s="3">
+        <v>82460.000</v>
+      </c>
+      <c r="E661" s="3">
+        <v>5600.000</v>
+      </c>
+      <c r="F661" s="3">
+        <v>778260.000</v>
+      </c>
+      <c r="G661" s="4">
+        <v>5.350570</v>
+      </c>
+      <c r="H661" s="4">
+        <v>0.037920</v>
+      </c>
+      <c r="I661" s="4">
+        <v>0.639400</v>
+      </c>
+      <c r="J661" s="4">
+        <v>0.042080</v>
+      </c>
+      <c r="K661" s="3">
+        <v>6.070</v>
+      </c>
+    </row>
+    <row r="662" spans="1:11">
+      <c r="A662" s="2">
+        <v>46233</v>
+      </c>
+      <c r="B662" s="3">
+        <v>692300.000</v>
+      </c>
+      <c r="C662" s="3">
+        <v>9660.000</v>
+      </c>
+      <c r="D662" s="3">
+        <v>85260.000</v>
+      </c>
+      <c r="E662" s="3">
+        <v>3780.000</v>
+      </c>
+      <c r="F662" s="3">
+        <v>791000.000</v>
+      </c>
+      <c r="G662" s="4">
+        <v>5.400740</v>
+      </c>
+      <c r="H662" s="4">
+        <v>0.074990</v>
+      </c>
+      <c r="I662" s="4">
+        <v>0.661140</v>
+      </c>
+      <c r="J662" s="4">
+        <v>0.029300</v>
+      </c>
+      <c r="K662" s="3">
+        <v>6.166</v>
+      </c>
+    </row>
+    <row r="663" spans="1:11">
+      <c r="A663" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B663" s="3">
+        <v>681940.000</v>
+      </c>
+      <c r="C663" s="3">
+        <v>9240.000</v>
+      </c>
+      <c r="D663" s="3">
+        <v>83720.000</v>
+      </c>
+      <c r="E663" s="3">
+        <v>4900.000</v>
+      </c>
+      <c r="F663" s="3">
+        <v>779800.000</v>
+      </c>
+      <c r="G663" s="4">
+        <v>5.311960</v>
+      </c>
+      <c r="H663" s="4">
+        <v>0.071480</v>
+      </c>
+      <c r="I663" s="4">
+        <v>0.646860</v>
+      </c>
+      <c r="J663" s="4">
+        <v>0.038060</v>
+      </c>
+      <c r="K663" s="3">
+        <v>6.068</v>
+      </c>
+    </row>
+    <row r="664" spans="1:11">
+      <c r="A664" s="2">
+        <v>46235</v>
+      </c>
+      <c r="B664" s="3">
+        <v>397420.000</v>
+      </c>
+      <c r="C664" s="3">
         <v>0.000</v>
       </c>
-      <c r="D656" s="3">
-        <v>19600.000</v>
-      </c>
-      <c r="E656" s="3">
+      <c r="D664" s="3">
+        <v>94920.000</v>
+      </c>
+      <c r="E664" s="3">
+        <v>3640.000</v>
+      </c>
+      <c r="F664" s="3">
+        <v>495980.000</v>
+      </c>
+      <c r="G664" s="4">
+        <v>3.093940</v>
+      </c>
+      <c r="H664" s="4">
+        <v>0.000000</v>
+      </c>
+      <c r="I664" s="4">
+        <v>0.732060</v>
+      </c>
+      <c r="J664" s="4">
+        <v>0.027090</v>
+      </c>
+      <c r="K664" s="3">
+        <v>3.853</v>
+      </c>
+    </row>
+    <row r="665" spans="1:11">
+      <c r="A665" s="2">
+        <v>46236</v>
+      </c>
+      <c r="B665" s="3">
+        <v>339500.000</v>
+      </c>
+      <c r="C665" s="3">
+        <v>5740.000</v>
+      </c>
+      <c r="D665" s="3">
+        <v>236180.000</v>
+      </c>
+      <c r="E665" s="3">
+        <v>12880.000</v>
+      </c>
+      <c r="F665" s="3">
+        <v>594300.000</v>
+      </c>
+      <c r="G665" s="4">
+        <v>2.629810</v>
+      </c>
+      <c r="H665" s="4">
+        <v>0.044200</v>
+      </c>
+      <c r="I665" s="4">
+        <v>1.805620</v>
+      </c>
+      <c r="J665" s="4">
+        <v>0.095690</v>
+      </c>
+      <c r="K665" s="3">
+        <v>4.575</v>
+      </c>
+    </row>
+    <row r="666" spans="1:11">
+      <c r="A666" s="2">
+        <v>46237</v>
+      </c>
+      <c r="B666" s="3">
+        <v>635320.000</v>
+      </c>
+      <c r="C666" s="3">
+        <v>5460.000</v>
+      </c>
+      <c r="D666" s="3">
+        <v>111780.000</v>
+      </c>
+      <c r="E666" s="3">
+        <v>0.000</v>
+      </c>
+      <c r="F666" s="3">
+        <v>752560.000</v>
+      </c>
+      <c r="G666" s="4">
+        <v>4.948920</v>
+      </c>
+      <c r="H666" s="4">
+        <v>0.042240</v>
+      </c>
+      <c r="I666" s="4">
+        <v>0.863610</v>
+      </c>
+      <c r="J666" s="4">
+        <v>0.000000</v>
+      </c>
+      <c r="K666" s="3">
+        <v>5.855</v>
+      </c>
+    </row>
+    <row r="667" spans="1:11">
+      <c r="A667" s="2">
+        <v>46238</v>
+      </c>
+      <c r="B667" s="3">
+        <v>656880.000</v>
+      </c>
+      <c r="C667" s="3">
+        <v>9100.000</v>
+      </c>
+      <c r="D667" s="3">
+        <v>102620.000</v>
+      </c>
+      <c r="E667" s="3">
+        <v>3920.000</v>
+      </c>
+      <c r="F667" s="3">
+        <v>772520.000</v>
+      </c>
+      <c r="G667" s="4">
+        <v>5.112410</v>
+      </c>
+      <c r="H667" s="4">
+        <v>0.070580</v>
+      </c>
+      <c r="I667" s="4">
+        <v>0.792670</v>
+      </c>
+      <c r="J667" s="4">
+        <v>0.030250</v>
+      </c>
+      <c r="K667" s="3">
+        <v>6.006</v>
+      </c>
+    </row>
+    <row r="668" spans="1:11">
+      <c r="A668" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B668" s="3">
+        <v>488040.000</v>
+      </c>
+      <c r="C668" s="3">
+        <v>6860.000</v>
+      </c>
+      <c r="D668" s="3">
+        <v>233900.000</v>
+      </c>
+      <c r="E668" s="3">
+        <v>11760.000</v>
+      </c>
+      <c r="F668" s="3">
+        <v>740560.000</v>
+      </c>
+      <c r="G668" s="4">
+        <v>3.779090</v>
+      </c>
+      <c r="H668" s="4">
+        <v>0.053000</v>
+      </c>
+      <c r="I668" s="4">
+        <v>1.798900</v>
+      </c>
+      <c r="J668" s="4">
+        <v>0.088200</v>
+      </c>
+      <c r="K668" s="3">
+        <v>5.719</v>
+      </c>
+    </row>
+    <row r="669" spans="1:11">
+      <c r="A669" s="2">
+        <v>46240</v>
+      </c>
+      <c r="B669" s="3">
+        <v>536900.000</v>
+      </c>
+      <c r="C669" s="3">
+        <v>7840.000</v>
+      </c>
+      <c r="D669" s="3">
+        <v>169540.000</v>
+      </c>
+      <c r="E669" s="3">
+        <v>3780.000</v>
+      </c>
+      <c r="F669" s="3">
+        <v>718060.000</v>
+      </c>
+      <c r="G669" s="4">
+        <v>4.170340</v>
+      </c>
+      <c r="H669" s="4">
+        <v>0.060560</v>
+      </c>
+      <c r="I669" s="4">
+        <v>1.303460</v>
+      </c>
+      <c r="J669" s="4">
+        <v>0.029060</v>
+      </c>
+      <c r="K669" s="3">
+        <v>5.563</v>
+      </c>
+    </row>
+    <row r="670" spans="1:11">
+      <c r="A670" s="2">
+        <v>46241</v>
+      </c>
+      <c r="B670" s="3">
+        <v>649460.000</v>
+      </c>
+      <c r="C670" s="3">
+        <v>9240.000</v>
+      </c>
+      <c r="D670" s="3">
+        <v>59700.000</v>
+      </c>
+      <c r="E670" s="3">
+        <v>3920.000</v>
+      </c>
+      <c r="F670" s="3">
+        <v>722320.000</v>
+      </c>
+      <c r="G670" s="4">
+        <v>5.069000</v>
+      </c>
+      <c r="H670" s="4">
+        <v>0.071750</v>
+      </c>
+      <c r="I670" s="4">
+        <v>0.462990</v>
+      </c>
+      <c r="J670" s="4">
+        <v>0.029460</v>
+      </c>
+      <c r="K670" s="3">
+        <v>5.633</v>
+      </c>
+    </row>
+    <row r="671" spans="1:11">
+      <c r="A671" s="2">
+        <v>46242</v>
+      </c>
+      <c r="B671" s="3">
+        <v>637560.000</v>
+      </c>
+      <c r="C671" s="3">
+        <v>8260.000</v>
+      </c>
+      <c r="D671" s="3">
+        <v>63980.000</v>
+      </c>
+      <c r="E671" s="3">
+        <v>5460.000</v>
+      </c>
+      <c r="F671" s="3">
+        <v>715260.000</v>
+      </c>
+      <c r="G671" s="4">
+        <v>4.979480</v>
+      </c>
+      <c r="H671" s="4">
+        <v>0.063840</v>
+      </c>
+      <c r="I671" s="4">
+        <v>0.494950</v>
+      </c>
+      <c r="J671" s="4">
+        <v>0.042020</v>
+      </c>
+      <c r="K671" s="3">
+        <v>5.580</v>
+      </c>
+    </row>
+    <row r="672" spans="1:11">
+      <c r="A672" s="2">
+        <v>46243</v>
+      </c>
+      <c r="B672" s="3">
+        <v>704480.000</v>
+      </c>
+      <c r="C672" s="3">
+        <v>9520.000</v>
+      </c>
+      <c r="D672" s="3">
+        <v>61180.000</v>
+      </c>
+      <c r="E672" s="3">
+        <v>3920.000</v>
+      </c>
+      <c r="F672" s="3">
+        <v>779100.000</v>
+      </c>
+      <c r="G672" s="4">
+        <v>5.501640</v>
+      </c>
+      <c r="H672" s="4">
+        <v>0.073940</v>
+      </c>
+      <c r="I672" s="4">
+        <v>0.472940</v>
+      </c>
+      <c r="J672" s="4">
+        <v>0.030050</v>
+      </c>
+      <c r="K672" s="3">
+        <v>6.079</v>
+      </c>
+    </row>
+    <row r="673" spans="1:11">
+      <c r="A673" s="2">
+        <v>46244</v>
+      </c>
+      <c r="B673" s="3">
+        <v>713720.000</v>
+      </c>
+      <c r="C673" s="3">
+        <v>8960.000</v>
+      </c>
+      <c r="D673" s="3">
+        <v>62160.000</v>
+      </c>
+      <c r="E673" s="3">
+        <v>3640.000</v>
+      </c>
+      <c r="F673" s="3">
+        <v>788480.000</v>
+      </c>
+      <c r="G673" s="4">
+        <v>5.575300</v>
+      </c>
+      <c r="H673" s="4">
+        <v>0.069570</v>
+      </c>
+      <c r="I673" s="4">
+        <v>0.481270</v>
+      </c>
+      <c r="J673" s="4">
+        <v>0.027610</v>
+      </c>
+      <c r="K673" s="3">
+        <v>6.154</v>
+      </c>
+    </row>
+    <row r="674" spans="1:11">
+      <c r="A674" s="2">
+        <v>46245</v>
+      </c>
+      <c r="B674" s="3">
+        <v>644980.000</v>
+      </c>
+      <c r="C674" s="3">
+        <v>2940.000</v>
+      </c>
+      <c r="D674" s="3">
+        <v>79800.000</v>
+      </c>
+      <c r="E674" s="3">
+        <v>6580.000</v>
+      </c>
+      <c r="F674" s="3">
+        <v>734300.000</v>
+      </c>
+      <c r="G674" s="4">
+        <v>5.036550</v>
+      </c>
+      <c r="H674" s="4">
+        <v>0.022790</v>
+      </c>
+      <c r="I674" s="4">
+        <v>0.617220</v>
+      </c>
+      <c r="J674" s="4">
+        <v>0.050620</v>
+      </c>
+      <c r="K674" s="3">
+        <v>5.727</v>
+      </c>
+    </row>
+    <row r="675" spans="1:11">
+      <c r="A675" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B675" s="3">
+        <v>707000.000</v>
+      </c>
+      <c r="C675" s="3">
+        <v>5180.000</v>
+      </c>
+      <c r="D675" s="3">
+        <v>50820.000</v>
+      </c>
+      <c r="E675" s="3">
+        <v>6720.000</v>
+      </c>
+      <c r="F675" s="3">
+        <v>769720.000</v>
+      </c>
+      <c r="G675" s="4">
+        <v>5.519360</v>
+      </c>
+      <c r="H675" s="4">
+        <v>0.040190</v>
+      </c>
+      <c r="I675" s="4">
+        <v>0.392770</v>
+      </c>
+      <c r="J675" s="4">
+        <v>0.051700</v>
+      </c>
+      <c r="K675" s="3">
+        <v>6.004</v>
+      </c>
+    </row>
+    <row r="676" spans="1:11">
+      <c r="A676" s="2">
+        <v>46247</v>
+      </c>
+      <c r="B676" s="3">
+        <v>704340.000</v>
+      </c>
+      <c r="C676" s="3">
+        <v>3780.000</v>
+      </c>
+      <c r="D676" s="3">
+        <v>58520.000</v>
+      </c>
+      <c r="E676" s="3">
+        <v>9100.000</v>
+      </c>
+      <c r="F676" s="3">
+        <v>775740.000</v>
+      </c>
+      <c r="G676" s="4">
+        <v>5.491140</v>
+      </c>
+      <c r="H676" s="4">
+        <v>0.029420</v>
+      </c>
+      <c r="I676" s="4">
+        <v>0.452270</v>
+      </c>
+      <c r="J676" s="4">
+        <v>0.070400</v>
+      </c>
+      <c r="K676" s="3">
+        <v>6.043</v>
+      </c>
+    </row>
+    <row r="677" spans="1:11">
+      <c r="A677" s="2">
+        <v>46248</v>
+      </c>
+      <c r="B677" s="3">
+        <v>680120.000</v>
+      </c>
+      <c r="C677" s="3">
+        <v>3360.000</v>
+      </c>
+      <c r="D677" s="3">
+        <v>74400.000</v>
+      </c>
+      <c r="E677" s="3">
+        <v>5180.000</v>
+      </c>
+      <c r="F677" s="3">
+        <v>763060.000</v>
+      </c>
+      <c r="G677" s="4">
+        <v>5.291780</v>
+      </c>
+      <c r="H677" s="4">
+        <v>0.025920</v>
+      </c>
+      <c r="I677" s="4">
+        <v>0.575490</v>
+      </c>
+      <c r="J677" s="4">
+        <v>0.039380</v>
+      </c>
+      <c r="K677" s="3">
+        <v>5.933</v>
+      </c>
+    </row>
+    <row r="678" spans="1:11">
+      <c r="A678" s="2">
+        <v>46249</v>
+      </c>
+      <c r="B678" s="3">
+        <v>559300.000</v>
+      </c>
+      <c r="C678" s="3">
+        <v>4760.000</v>
+      </c>
+      <c r="D678" s="3">
+        <v>192500.000</v>
+      </c>
+      <c r="E678" s="3">
+        <v>5880.000</v>
+      </c>
+      <c r="F678" s="3">
+        <v>762440.000</v>
+      </c>
+      <c r="G678" s="4">
+        <v>4.342810</v>
+      </c>
+      <c r="H678" s="4">
+        <v>0.036890</v>
+      </c>
+      <c r="I678" s="4">
+        <v>1.485900</v>
+      </c>
+      <c r="J678" s="4">
+        <v>0.045220</v>
+      </c>
+      <c r="K678" s="3">
+        <v>5.911</v>
+      </c>
+    </row>
+    <row r="679" spans="1:11">
+      <c r="A679" s="2">
+        <v>46250</v>
+      </c>
+      <c r="B679" s="3">
+        <v>574980.000</v>
+      </c>
+      <c r="C679" s="3">
+        <v>5040.000</v>
+      </c>
+      <c r="D679" s="3">
+        <v>137900.000</v>
+      </c>
+      <c r="E679" s="3">
+        <v>5460.000</v>
+      </c>
+      <c r="F679" s="3">
+        <v>723380.000</v>
+      </c>
+      <c r="G679" s="4">
+        <v>4.467210</v>
+      </c>
+      <c r="H679" s="4">
+        <v>0.039140</v>
+      </c>
+      <c r="I679" s="4">
+        <v>1.063220</v>
+      </c>
+      <c r="J679" s="4">
+        <v>0.041180</v>
+      </c>
+      <c r="K679" s="3">
+        <v>5.611</v>
+      </c>
+    </row>
+    <row r="680" spans="1:11">
+      <c r="A680" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B680" s="3">
+        <v>669480.000</v>
+      </c>
+      <c r="C680" s="3">
+        <v>3780.000</v>
+      </c>
+      <c r="D680" s="3">
+        <v>75740.000</v>
+      </c>
+      <c r="E680" s="3">
+        <v>3500.000</v>
+      </c>
+      <c r="F680" s="3">
+        <v>752500.000</v>
+      </c>
+      <c r="G680" s="4">
+        <v>5.208330</v>
+      </c>
+      <c r="H680" s="4">
+        <v>0.029170</v>
+      </c>
+      <c r="I680" s="4">
+        <v>0.584950</v>
+      </c>
+      <c r="J680" s="4">
+        <v>0.026820</v>
+      </c>
+      <c r="K680" s="3">
+        <v>5.849</v>
+      </c>
+    </row>
+    <row r="681" spans="1:11">
+      <c r="A681" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B681" s="3">
+        <v>704760.000</v>
+      </c>
+      <c r="C681" s="3">
+        <v>5600.000</v>
+      </c>
+      <c r="D681" s="3">
+        <v>51800.000</v>
+      </c>
+      <c r="E681" s="3">
+        <v>4760.000</v>
+      </c>
+      <c r="F681" s="3">
+        <v>766920.000</v>
+      </c>
+      <c r="G681" s="4">
+        <v>5.488620</v>
+      </c>
+      <c r="H681" s="4">
+        <v>0.043370</v>
+      </c>
+      <c r="I681" s="4">
+        <v>0.399780</v>
+      </c>
+      <c r="J681" s="4">
+        <v>0.036350</v>
+      </c>
+      <c r="K681" s="3">
+        <v>5.968</v>
+      </c>
+    </row>
+    <row r="682" spans="1:11">
+      <c r="A682" s="2">
+        <v>46253</v>
+      </c>
+      <c r="B682" s="3">
+        <v>691320.000</v>
+      </c>
+      <c r="C682" s="3">
+        <v>1540.000</v>
+      </c>
+      <c r="D682" s="3">
+        <v>45780.000</v>
+      </c>
+      <c r="E682" s="3">
+        <v>4900.000</v>
+      </c>
+      <c r="F682" s="3">
+        <v>743540.000</v>
+      </c>
+      <c r="G682" s="4">
+        <v>5.386230</v>
+      </c>
+      <c r="H682" s="4">
+        <v>0.011860</v>
+      </c>
+      <c r="I682" s="4">
+        <v>0.353460</v>
+      </c>
+      <c r="J682" s="4">
+        <v>0.036960</v>
+      </c>
+      <c r="K682" s="3">
+        <v>5.789</v>
+      </c>
+    </row>
+    <row r="683" spans="1:11">
+      <c r="A683" s="2">
+        <v>46254</v>
+      </c>
+      <c r="B683" s="3">
+        <v>650440.000</v>
+      </c>
+      <c r="C683" s="3">
+        <v>4340.000</v>
+      </c>
+      <c r="D683" s="3">
+        <v>35400.000</v>
+      </c>
+      <c r="E683" s="3">
+        <v>4900.000</v>
+      </c>
+      <c r="F683" s="3">
+        <v>695080.000</v>
+      </c>
+      <c r="G683" s="4">
+        <v>5.074150</v>
+      </c>
+      <c r="H683" s="4">
+        <v>0.033670</v>
+      </c>
+      <c r="I683" s="4">
+        <v>0.273130</v>
+      </c>
+      <c r="J683" s="4">
+        <v>0.037790</v>
+      </c>
+      <c r="K683" s="3">
+        <v>5.419</v>
+      </c>
+    </row>
+    <row r="684" spans="1:11">
+      <c r="A684" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B684" s="3">
+        <v>712040.000</v>
+      </c>
+      <c r="C684" s="3">
+        <v>1400.000</v>
+      </c>
+      <c r="D684" s="3">
+        <v>37240.000</v>
+      </c>
+      <c r="E684" s="3">
+        <v>4900.000</v>
+      </c>
+      <c r="F684" s="3">
+        <v>755580.000</v>
+      </c>
+      <c r="G684" s="4">
+        <v>5.550850</v>
+      </c>
+      <c r="H684" s="4">
+        <v>0.010970</v>
+      </c>
+      <c r="I684" s="4">
+        <v>0.287540</v>
+      </c>
+      <c r="J684" s="4">
+        <v>0.037500</v>
+      </c>
+      <c r="K684" s="3">
+        <v>5.887</v>
+      </c>
+    </row>
+    <row r="685" spans="1:11">
+      <c r="A685" s="2">
+        <v>46256</v>
+      </c>
+      <c r="B685" s="3">
+        <v>679560.000</v>
+      </c>
+      <c r="C685" s="3">
+        <v>1400.000</v>
+      </c>
+      <c r="D685" s="3">
+        <v>52360.000</v>
+      </c>
+      <c r="E685" s="3">
+        <v>4340.000</v>
+      </c>
+      <c r="F685" s="3">
+        <v>737660.000</v>
+      </c>
+      <c r="G685" s="4">
+        <v>5.294430</v>
+      </c>
+      <c r="H685" s="4">
+        <v>0.010780</v>
+      </c>
+      <c r="I685" s="4">
+        <v>0.403060</v>
+      </c>
+      <c r="J685" s="4">
+        <v>0.033310</v>
+      </c>
+      <c r="K685" s="3">
+        <v>5.742</v>
+      </c>
+    </row>
+    <row r="686" spans="1:11">
+      <c r="A686" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B686" s="3">
+        <v>726180.000</v>
+      </c>
+      <c r="C686" s="3">
+        <v>5180.000</v>
+      </c>
+      <c r="D686" s="3">
+        <v>46760.000</v>
+      </c>
+      <c r="E686" s="3">
+        <v>6160.000</v>
+      </c>
+      <c r="F686" s="3">
+        <v>784280.000</v>
+      </c>
+      <c r="G686" s="4">
+        <v>5.655380</v>
+      </c>
+      <c r="H686" s="4">
+        <v>0.040200</v>
+      </c>
+      <c r="I686" s="4">
+        <v>0.359380</v>
+      </c>
+      <c r="J686" s="4">
+        <v>0.047120</v>
+      </c>
+      <c r="K686" s="3">
+        <v>6.102</v>
+      </c>
+    </row>
+    <row r="687" spans="1:11">
+      <c r="A687" s="2">
+        <v>46258</v>
+      </c>
+      <c r="B687" s="3">
+        <v>656320.000</v>
+      </c>
+      <c r="C687" s="3">
+        <v>1400.000</v>
+      </c>
+      <c r="D687" s="3">
+        <v>93800.000</v>
+      </c>
+      <c r="E687" s="3">
+        <v>3780.000</v>
+      </c>
+      <c r="F687" s="3">
+        <v>755300.000</v>
+      </c>
+      <c r="G687" s="4">
+        <v>5.101120</v>
+      </c>
+      <c r="H687" s="4">
+        <v>0.010830</v>
+      </c>
+      <c r="I687" s="4">
+        <v>0.722160</v>
+      </c>
+      <c r="J687" s="4">
+        <v>0.028970</v>
+      </c>
+      <c r="K687" s="3">
+        <v>5.863</v>
+      </c>
+    </row>
+    <row r="688" spans="1:11">
+      <c r="A688" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B688" s="3">
+        <v>682360.000</v>
+      </c>
+      <c r="C688" s="3">
+        <v>4340.000</v>
+      </c>
+      <c r="D688" s="3">
+        <v>95060.000</v>
+      </c>
+      <c r="E688" s="3">
+        <v>6300.000</v>
+      </c>
+      <c r="F688" s="3">
+        <v>788060.000</v>
+      </c>
+      <c r="G688" s="4">
+        <v>5.308510</v>
+      </c>
+      <c r="H688" s="4">
+        <v>0.033670</v>
+      </c>
+      <c r="I688" s="4">
+        <v>0.732140</v>
+      </c>
+      <c r="J688" s="4">
+        <v>0.048680</v>
+      </c>
+      <c r="K688" s="3">
+        <v>6.123</v>
+      </c>
+    </row>
+    <row r="689" spans="1:11">
+      <c r="A689" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B689" s="3">
+        <v>691320.000</v>
+      </c>
+      <c r="C689" s="3">
+        <v>2800.000</v>
+      </c>
+      <c r="D689" s="3">
+        <v>64960.000</v>
+      </c>
+      <c r="E689" s="3">
+        <v>6440.000</v>
+      </c>
+      <c r="F689" s="3">
+        <v>765520.000</v>
+      </c>
+      <c r="G689" s="4">
+        <v>5.379510</v>
+      </c>
+      <c r="H689" s="4">
+        <v>0.021610</v>
+      </c>
+      <c r="I689" s="4">
+        <v>0.501030</v>
+      </c>
+      <c r="J689" s="4">
+        <v>0.048840</v>
+      </c>
+      <c r="K689" s="3">
+        <v>5.951</v>
+      </c>
+    </row>
+    <row r="690" spans="1:11">
+      <c r="A690" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B690" s="3">
+        <v>624820.000</v>
+      </c>
+      <c r="C690" s="3">
+        <v>1400.000</v>
+      </c>
+      <c r="D690" s="3">
+        <v>95200.000</v>
+      </c>
+      <c r="E690" s="3">
+        <v>6300.000</v>
+      </c>
+      <c r="F690" s="3">
+        <v>727720.000</v>
+      </c>
+      <c r="G690" s="4">
+        <v>4.852480</v>
+      </c>
+      <c r="H690" s="4">
+        <v>0.010780</v>
+      </c>
+      <c r="I690" s="4">
+        <v>0.732510</v>
+      </c>
+      <c r="J690" s="4">
+        <v>0.047740</v>
+      </c>
+      <c r="K690" s="3">
+        <v>5.644</v>
+      </c>
+    </row>
+    <row r="691" spans="1:11">
+      <c r="A691" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B691" s="3">
+        <v>625380.000</v>
+      </c>
+      <c r="C691" s="3">
+        <v>1820.000</v>
+      </c>
+      <c r="D691" s="3">
+        <v>79800.000</v>
+      </c>
+      <c r="E691" s="3">
+        <v>9240.000</v>
+      </c>
+      <c r="F691" s="3">
+        <v>716240.000</v>
+      </c>
+      <c r="G691" s="4">
+        <v>4.858180</v>
+      </c>
+      <c r="H691" s="4">
+        <v>0.014010</v>
+      </c>
+      <c r="I691" s="4">
+        <v>0.614610</v>
+      </c>
+      <c r="J691" s="4">
+        <v>0.071370</v>
+      </c>
+      <c r="K691" s="3">
+        <v>5.558</v>
+      </c>
+    </row>
+    <row r="692" spans="1:11">
+      <c r="A692" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B692" s="3">
+        <v>694120.000</v>
+      </c>
+      <c r="C692" s="3">
+        <v>2940.000</v>
+      </c>
+      <c r="D692" s="3">
+        <v>56140.000</v>
+      </c>
+      <c r="E692" s="3">
+        <v>14840.000</v>
+      </c>
+      <c r="F692" s="3">
+        <v>768040.000</v>
+      </c>
+      <c r="G692" s="4">
+        <v>5.399880</v>
+      </c>
+      <c r="H692" s="4">
+        <v>0.022880</v>
+      </c>
+      <c r="I692" s="4">
+        <v>0.431770</v>
+      </c>
+      <c r="J692" s="4">
+        <v>0.114200</v>
+      </c>
+      <c r="K692" s="3">
+        <v>5.969</v>
+      </c>
+    </row>
+    <row r="693" spans="1:11">
+      <c r="A693" s="2">
+        <v>46264</v>
+      </c>
+      <c r="B693" s="3">
+        <v>710360.000</v>
+      </c>
+      <c r="C693" s="3">
+        <v>3360.000</v>
+      </c>
+      <c r="D693" s="3">
+        <v>43680.000</v>
+      </c>
+      <c r="E693" s="3">
+        <v>9240.000</v>
+      </c>
+      <c r="F693" s="3">
+        <v>766640.000</v>
+      </c>
+      <c r="G693" s="4">
+        <v>5.536550</v>
+      </c>
+      <c r="H693" s="4">
+        <v>0.025920</v>
+      </c>
+      <c r="I693" s="4">
+        <v>0.335780</v>
+      </c>
+      <c r="J693" s="4">
+        <v>0.071360</v>
+      </c>
+      <c r="K693" s="3">
+        <v>5.970</v>
+      </c>
+    </row>
+    <row r="694" spans="1:11">
+      <c r="A694" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B694" s="3">
+        <v>735840.000</v>
+      </c>
+      <c r="C694" s="3">
+        <v>4200.000</v>
+      </c>
+      <c r="D694" s="3">
+        <v>31500.000</v>
+      </c>
+      <c r="E694" s="3">
+        <v>7280.000</v>
+      </c>
+      <c r="F694" s="3">
+        <v>778820.000</v>
+      </c>
+      <c r="G694" s="4">
+        <v>5.738020</v>
+      </c>
+      <c r="H694" s="4">
+        <v>0.032570</v>
+      </c>
+      <c r="I694" s="4">
+        <v>0.242380</v>
+      </c>
+      <c r="J694" s="4">
+        <v>0.056260</v>
+      </c>
+      <c r="K694" s="3">
+        <v>6.069</v>
+      </c>
+    </row>
+    <row r="695" spans="1:11">
+      <c r="A695" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B695" s="3">
+        <v>498960.000</v>
+      </c>
+      <c r="C695" s="3">
+        <v>0.000</v>
+      </c>
+      <c r="D695" s="3">
+        <v>21560.000</v>
+      </c>
+      <c r="E695" s="3">
         <v>1960.000</v>
       </c>
-      <c r="F656" s="3">
-        <v>468300.000</v>
-      </c>
-      <c r="G656" s="4">
-        <v>3.485950</v>
-      </c>
-      <c r="H656" s="4">
+      <c r="F695" s="3">
+        <v>522480.000</v>
+      </c>
+      <c r="G695" s="4">
+        <v>3.888690</v>
+      </c>
+      <c r="H695" s="4">
         <v>0.000000</v>
       </c>
-      <c r="I656" s="4">
-        <v>0.152290</v>
-      </c>
-      <c r="J656" s="4">
-        <v>0.015220</v>
-      </c>
-      <c r="K656" s="3">
-        <v>3.653</v>
+      <c r="I695" s="4">
+        <v>0.165550</v>
+      </c>
+      <c r="J695" s="4">
+        <v>0.015290</v>
+      </c>
+      <c r="K695" s="3">
+        <v>4.070</v>
+      </c>
+    </row>
+    <row r="696" spans="1:11">
+      <c r="A696" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B696" s="3">
+        <v>888720.000</v>
+      </c>
+      <c r="C696" s="3">
+        <v>7280.000</v>
+      </c>
+      <c r="D696" s="3">
+        <v>48860.000</v>
+      </c>
+      <c r="E696" s="3">
+        <v>18340.000</v>
+      </c>
+      <c r="F696" s="3">
+        <v>963200.000</v>
+      </c>
+      <c r="G696" s="4">
+        <v>6.926640</v>
+      </c>
+      <c r="H696" s="4">
+        <v>0.056510</v>
+      </c>
+      <c r="I696" s="4">
+        <v>0.376110</v>
+      </c>
+      <c r="J696" s="4">
+        <v>0.141040</v>
+      </c>
+      <c r="K696" s="3">
+        <v>7.500</v>
+      </c>
+    </row>
+    <row r="697" spans="1:11">
+      <c r="A697" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B697" s="3">
+        <v>690760.000</v>
+      </c>
+      <c r="C697" s="3">
+        <v>0.000</v>
+      </c>
+      <c r="D697" s="3">
+        <v>29400.000</v>
+      </c>
+      <c r="E697" s="3">
+        <v>7420.000</v>
+      </c>
+      <c r="F697" s="3">
+        <v>727580.000</v>
+      </c>
+      <c r="G697" s="4">
+        <v>5.389240</v>
+      </c>
+      <c r="H697" s="4">
+        <v>0.000000</v>
+      </c>
+      <c r="I697" s="4">
+        <v>0.225870</v>
+      </c>
+      <c r="J697" s="4">
+        <v>0.057690</v>
+      </c>
+      <c r="K697" s="3">
+        <v>5.673</v>
+      </c>
+    </row>
+    <row r="698" spans="1:11">
+      <c r="A698" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B698" s="3">
+        <v>745360.000</v>
+      </c>
+      <c r="C698" s="3">
+        <v>6440.000</v>
+      </c>
+      <c r="D698" s="3">
+        <v>22120.000</v>
+      </c>
+      <c r="E698" s="3">
+        <v>3360.000</v>
+      </c>
+      <c r="F698" s="3">
+        <v>777280.000</v>
+      </c>
+      <c r="G698" s="4">
+        <v>5.820160</v>
+      </c>
+      <c r="H698" s="4">
+        <v>0.050040</v>
+      </c>
+      <c r="I698" s="4">
+        <v>0.170480</v>
+      </c>
+      <c r="J698" s="4">
+        <v>0.026160</v>
+      </c>
+      <c r="K698" s="3">
+        <v>6.067</v>
+      </c>
+    </row>
+    <row r="699" spans="1:11">
+      <c r="A699" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B699" s="3">
+        <v>690200.000</v>
+      </c>
+      <c r="C699" s="3">
+        <v>4340.000</v>
+      </c>
+      <c r="D699" s="3">
+        <v>29960.000</v>
+      </c>
+      <c r="E699" s="3">
+        <v>7840.000</v>
+      </c>
+      <c r="F699" s="3">
+        <v>732340.000</v>
+      </c>
+      <c r="G699" s="4">
+        <v>5.387640</v>
+      </c>
+      <c r="H699" s="4">
+        <v>0.033610</v>
+      </c>
+      <c r="I699" s="4">
+        <v>0.230150</v>
+      </c>
+      <c r="J699" s="4">
+        <v>0.060530</v>
+      </c>
+      <c r="K699" s="3">
+        <v>5.712</v>
+      </c>
+    </row>
+    <row r="700" spans="1:11">
+      <c r="A700" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B700" s="3">
+        <v>712320.000</v>
+      </c>
+      <c r="C700" s="3">
+        <v>5040.000</v>
+      </c>
+      <c r="D700" s="3">
+        <v>50820.000</v>
+      </c>
+      <c r="E700" s="3">
+        <v>6720.000</v>
+      </c>
+      <c r="F700" s="3">
+        <v>774900.000</v>
+      </c>
+      <c r="G700" s="4">
+        <v>5.536070</v>
+      </c>
+      <c r="H700" s="4">
+        <v>0.039070</v>
+      </c>
+      <c r="I700" s="4">
+        <v>0.389630</v>
+      </c>
+      <c r="J700" s="4">
+        <v>0.050990</v>
+      </c>
+      <c r="K700" s="3">
+        <v>6.016</v>
+      </c>
+    </row>
+    <row r="701" spans="1:11">
+      <c r="A701" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B701" s="3">
+        <v>703080.000</v>
+      </c>
+      <c r="C701" s="3">
+        <v>1960.000</v>
+      </c>
+      <c r="D701" s="3">
+        <v>54180.000</v>
+      </c>
+      <c r="E701" s="3">
+        <v>9100.000</v>
+      </c>
+      <c r="F701" s="3">
+        <v>768320.000</v>
+      </c>
+      <c r="G701" s="4">
+        <v>5.444840</v>
+      </c>
+      <c r="H701" s="4">
+        <v>0.015090</v>
+      </c>
+      <c r="I701" s="4">
+        <v>0.415330</v>
+      </c>
+      <c r="J701" s="4">
+        <v>0.070240</v>
+      </c>
+      <c r="K701" s="3">
+        <v>5.946</v>
+      </c>
+    </row>
+    <row r="702" spans="1:11">
+      <c r="A702" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B702" s="3">
+        <v>698040.000</v>
+      </c>
+      <c r="C702" s="3">
+        <v>1960.000</v>
+      </c>
+      <c r="D702" s="3">
+        <v>70840.000</v>
+      </c>
+      <c r="E702" s="3">
+        <v>8120.000</v>
+      </c>
+      <c r="F702" s="3">
+        <v>778960.000</v>
+      </c>
+      <c r="G702" s="4">
+        <v>5.397800</v>
+      </c>
+      <c r="H702" s="4">
+        <v>0.015090</v>
+      </c>
+      <c r="I702" s="4">
+        <v>0.544060</v>
+      </c>
+      <c r="J702" s="4">
+        <v>0.061660</v>
+      </c>
+      <c r="K702" s="3">
+        <v>6.019</v>
+      </c>
+    </row>
+    <row r="703" spans="1:11">
+      <c r="A703" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B703" s="3">
+        <v>651840.000</v>
+      </c>
+      <c r="C703" s="3">
+        <v>7840.000</v>
+      </c>
+      <c r="D703" s="3">
+        <v>66500.000</v>
+      </c>
+      <c r="E703" s="3">
+        <v>6440.000</v>
+      </c>
+      <c r="F703" s="3">
+        <v>732620.000</v>
+      </c>
+      <c r="G703" s="4">
+        <v>5.041030</v>
+      </c>
+      <c r="H703" s="4">
+        <v>0.060560</v>
+      </c>
+      <c r="I703" s="4">
+        <v>0.510560</v>
+      </c>
+      <c r="J703" s="4">
+        <v>0.049090</v>
+      </c>
+      <c r="K703" s="3">
+        <v>5.661</v>
+      </c>
+    </row>
+    <row r="704" spans="1:11">
+      <c r="A704" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B704" s="3">
+        <v>574840.000</v>
+      </c>
+      <c r="C704" s="3">
+        <v>5880.000</v>
+      </c>
+      <c r="D704" s="3">
+        <v>178500.000</v>
+      </c>
+      <c r="E704" s="3">
+        <v>9660.000</v>
+      </c>
+      <c r="F704" s="3">
+        <v>768880.000</v>
+      </c>
+      <c r="G704" s="4">
+        <v>4.447360</v>
+      </c>
+      <c r="H704" s="4">
+        <v>0.045270</v>
+      </c>
+      <c r="I704" s="4">
+        <v>1.358880</v>
+      </c>
+      <c r="J704" s="4">
+        <v>0.072540</v>
+      </c>
+      <c r="K704" s="3">
+        <v>5.924</v>
+      </c>
+    </row>
+    <row r="705" spans="1:11">
+      <c r="A705" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B705" s="3">
+        <v>425040.000</v>
+      </c>
+      <c r="C705" s="3">
+        <v>5880.000</v>
+      </c>
+      <c r="D705" s="3">
+        <v>109060.000</v>
+      </c>
+      <c r="E705" s="3">
+        <v>7000.000</v>
+      </c>
+      <c r="F705" s="3">
+        <v>546980.000</v>
+      </c>
+      <c r="G705" s="4">
+        <v>3.282680</v>
+      </c>
+      <c r="H705" s="4">
+        <v>0.045340</v>
+      </c>
+      <c r="I705" s="4">
+        <v>0.834240</v>
+      </c>
+      <c r="J705" s="4">
+        <v>0.053070</v>
+      </c>
+      <c r="K705" s="3">
+        <v>4.215</v>
+      </c>
+    </row>
+    <row r="706" spans="1:11">
+      <c r="A706" s="2">
+        <v>46277</v>
+      </c>
+      <c r="B706" s="3">
+        <v>554960.000</v>
+      </c>
+      <c r="C706" s="3">
+        <v>5320.000</v>
+      </c>
+      <c r="D706" s="3">
+        <v>113540.000</v>
+      </c>
+      <c r="E706" s="3">
+        <v>11620.000</v>
+      </c>
+      <c r="F706" s="3">
+        <v>685440.000</v>
+      </c>
+      <c r="G706" s="4">
+        <v>4.271510</v>
+      </c>
+      <c r="H706" s="4">
+        <v>0.041100</v>
+      </c>
+      <c r="I706" s="4">
+        <v>0.865470</v>
+      </c>
+      <c r="J706" s="4">
+        <v>0.087960</v>
+      </c>
+      <c r="K706" s="3">
+        <v>5.266</v>
+      </c>
+    </row>
+    <row r="707" spans="1:11">
+      <c r="A707" s="2">
+        <v>46278</v>
+      </c>
+      <c r="B707" s="3">
+        <v>611240.000</v>
+      </c>
+      <c r="C707" s="3">
+        <v>10780.000</v>
+      </c>
+      <c r="D707" s="3">
+        <v>93380.000</v>
+      </c>
+      <c r="E707" s="3">
+        <v>7560.000</v>
+      </c>
+      <c r="F707" s="3">
+        <v>722960.000</v>
+      </c>
+      <c r="G707" s="4">
+        <v>4.708730</v>
+      </c>
+      <c r="H707" s="4">
+        <v>0.083160</v>
+      </c>
+      <c r="I707" s="4">
+        <v>0.710500</v>
+      </c>
+      <c r="J707" s="4">
+        <v>0.056750</v>
+      </c>
+      <c r="K707" s="3">
+        <v>5.559</v>
+      </c>
+    </row>
+    <row r="708" spans="1:11">
+      <c r="A708" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B708" s="3">
+        <v>708680.000</v>
+      </c>
+      <c r="C708" s="3">
+        <v>1960.000</v>
+      </c>
+      <c r="D708" s="3">
+        <v>31920.000</v>
+      </c>
+      <c r="E708" s="3">
+        <v>0.000</v>
+      </c>
+      <c r="F708" s="3">
+        <v>742560.000</v>
+      </c>
+      <c r="G708" s="4">
+        <v>5.510720</v>
+      </c>
+      <c r="H708" s="4">
+        <v>0.015090</v>
+      </c>
+      <c r="I708" s="4">
+        <v>0.243820</v>
+      </c>
+      <c r="J708" s="4">
+        <v>0.000000</v>
+      </c>
+      <c r="K708" s="3">
+        <v>5.770</v>
+      </c>
+    </row>
+    <row r="709" spans="1:11">
+      <c r="A709" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B709" s="3">
+        <v>654080.000</v>
+      </c>
+      <c r="C709" s="3">
+        <v>9660.000</v>
+      </c>
+      <c r="D709" s="3">
+        <v>17080.000</v>
+      </c>
+      <c r="E709" s="3">
+        <v>15680.000</v>
+      </c>
+      <c r="F709" s="3">
+        <v>696500.000</v>
+      </c>
+      <c r="G709" s="4">
+        <v>5.095770</v>
+      </c>
+      <c r="H709" s="4">
+        <v>0.074970</v>
+      </c>
+      <c r="I709" s="4">
+        <v>0.131290</v>
+      </c>
+      <c r="J709" s="4">
+        <v>0.121000</v>
+      </c>
+      <c r="K709" s="3">
+        <v>5.423</v>
+      </c>
+    </row>
+    <row r="710" spans="1:11">
+      <c r="A710" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B710" s="3">
+        <v>636800.000</v>
+      </c>
+      <c r="C710" s="3">
+        <v>5460.000</v>
+      </c>
+      <c r="D710" s="3">
+        <v>24640.000</v>
+      </c>
+      <c r="E710" s="3">
+        <v>3080.000</v>
+      </c>
+      <c r="F710" s="3">
+        <v>669980.000</v>
+      </c>
+      <c r="G710" s="4">
+        <v>4.954550</v>
+      </c>
+      <c r="H710" s="4">
+        <v>0.042440</v>
+      </c>
+      <c r="I710" s="4">
+        <v>0.188480</v>
+      </c>
+      <c r="J710" s="4">
+        <v>0.023040</v>
+      </c>
+      <c r="K710" s="3">
+        <v>5.209</v>
+      </c>
+    </row>
+    <row r="711" spans="1:11">
+      <c r="A711" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B711" s="3">
+        <v>520560.000</v>
+      </c>
+      <c r="C711" s="3">
+        <v>8260.000</v>
+      </c>
+      <c r="D711" s="3">
+        <v>34440.000</v>
+      </c>
+      <c r="E711" s="3">
+        <v>2940.000</v>
+      </c>
+      <c r="F711" s="3">
+        <v>566200.000</v>
+      </c>
+      <c r="G711" s="4">
+        <v>4.055410</v>
+      </c>
+      <c r="H711" s="4">
+        <v>0.063930</v>
+      </c>
+      <c r="I711" s="4">
+        <v>0.264260</v>
+      </c>
+      <c r="J711" s="4">
+        <v>0.021920</v>
+      </c>
+      <c r="K711" s="3">
+        <v>4.406</v>
+      </c>
+    </row>
+    <row r="712" spans="1:11">
+      <c r="A712" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B712" s="3">
+        <v>575680.000</v>
+      </c>
+      <c r="C712" s="3">
+        <v>5600.000</v>
+      </c>
+      <c r="D712" s="3">
+        <v>34020.000</v>
+      </c>
+      <c r="E712" s="3">
+        <v>1960.000</v>
+      </c>
+      <c r="F712" s="3">
+        <v>617260.000</v>
+      </c>
+      <c r="G712" s="4">
+        <v>4.481740</v>
+      </c>
+      <c r="H712" s="4">
+        <v>0.043490</v>
+      </c>
+      <c r="I712" s="4">
+        <v>0.260340</v>
+      </c>
+      <c r="J712" s="4">
+        <v>0.014370</v>
+      </c>
+      <c r="K712" s="3">
+        <v>4.800</v>
+      </c>
+    </row>
+    <row r="713" spans="1:11">
+      <c r="A713" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B713" s="3">
+        <v>302960.000</v>
+      </c>
+      <c r="C713" s="3">
+        <v>0.000</v>
+      </c>
+      <c r="D713" s="3">
+        <v>9800.000</v>
+      </c>
+      <c r="E713" s="3">
+        <v>1960.000</v>
+      </c>
+      <c r="F713" s="3">
+        <v>314720.000</v>
+      </c>
+      <c r="G713" s="4">
+        <v>2.356260</v>
+      </c>
+      <c r="H713" s="4">
+        <v>0.000000</v>
+      </c>
+      <c r="I713" s="4">
+        <v>0.075200</v>
+      </c>
+      <c r="J713" s="4">
+        <v>0.014830</v>
+      </c>
+      <c r="K713" s="3">
+        <v>2.446</v>
       </c>
     </row>
   </sheetData>

--- a/backend/data/Daywise MW Report.xlsx
+++ b/backend/data/Daywise MW Report.xlsx
@@ -910,13 +910,13 @@
         <v>45591</v>
       </c>
       <c r="B22" s="3">
-        <v>6720.000</v>
+        <v>8040.000</v>
       </c>
       <c r="C22" s="3">
         <v>0.000</v>
       </c>
       <c r="D22" s="3">
-        <v>65880.000</v>
+        <v>64560.000</v>
       </c>
       <c r="E22" s="3">
         <v>1680.000</v>
@@ -925,19 +925,19 @@
         <v>74280.000</v>
       </c>
       <c r="G22" s="4">
-        <v>0.050450</v>
+        <v>0.060340</v>
       </c>
       <c r="H22" s="4">
         <v>0.000000</v>
       </c>
       <c r="I22" s="4">
-        <v>0.483840</v>
+        <v>0.474660</v>
       </c>
       <c r="J22" s="4">
         <v>0.011690</v>
       </c>
       <c r="K22" s="3">
-        <v>0.546</v>
+        <v>0.547</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -980,13 +980,13 @@
         <v>45593</v>
       </c>
       <c r="B24" s="3">
-        <v>12480.000</v>
+        <v>14160.000</v>
       </c>
       <c r="C24" s="3">
         <v>10560.000</v>
       </c>
       <c r="D24" s="3">
-        <v>101400.000</v>
+        <v>99720.000</v>
       </c>
       <c r="E24" s="3">
         <v>3360.000</v>
@@ -995,13 +995,13 @@
         <v>127800.000</v>
       </c>
       <c r="G24" s="4">
-        <v>0.093390</v>
+        <v>0.105810</v>
       </c>
       <c r="H24" s="4">
         <v>0.076710</v>
       </c>
       <c r="I24" s="4">
-        <v>0.749050</v>
+        <v>0.736800</v>
       </c>
       <c r="J24" s="4">
         <v>0.023390</v>
@@ -1295,13 +1295,13 @@
         <v>45602</v>
       </c>
       <c r="B33" s="3">
-        <v>135480.000</v>
+        <v>136920.000</v>
       </c>
       <c r="C33" s="3">
         <v>1680.000</v>
       </c>
       <c r="D33" s="3">
-        <v>16680.000</v>
+        <v>15240.000</v>
       </c>
       <c r="E33" s="3">
         <v>0.000</v>
@@ -1310,13 +1310,13 @@
         <v>153840.000</v>
       </c>
       <c r="G33" s="4">
-        <v>1.022960</v>
+        <v>1.033610</v>
       </c>
       <c r="H33" s="4">
         <v>0.012640</v>
       </c>
       <c r="I33" s="4">
-        <v>0.124070</v>
+        <v>0.113280</v>
       </c>
       <c r="J33" s="4">
         <v>0.000000</v>
@@ -1470,10 +1470,10 @@
         <v>45607</v>
       </c>
       <c r="B38" s="3">
-        <v>143640.000</v>
+        <v>141960.000</v>
       </c>
       <c r="C38" s="3">
-        <v>23520.000</v>
+        <v>25200.000</v>
       </c>
       <c r="D38" s="3">
         <v>1680.000</v>
@@ -1485,10 +1485,10 @@
         <v>170400.000</v>
       </c>
       <c r="G38" s="4">
-        <v>1.084280</v>
+        <v>1.071530</v>
       </c>
       <c r="H38" s="4">
-        <v>0.173890</v>
+        <v>0.186360</v>
       </c>
       <c r="I38" s="4">
         <v>0.012420</v>
@@ -1590,7 +1590,7 @@
         <v>185880.000</v>
       </c>
       <c r="G41" s="4">
-        <v>1.168990</v>
+        <v>1.169190</v>
       </c>
       <c r="H41" s="4">
         <v>0.008350</v>
@@ -1695,7 +1695,7 @@
         <v>204360.000</v>
       </c>
       <c r="G44" s="4">
-        <v>1.160250</v>
+        <v>1.160290</v>
       </c>
       <c r="H44" s="4">
         <v>0.036970</v>
@@ -1785,13 +1785,13 @@
         <v>45616</v>
       </c>
       <c r="B47" s="3">
-        <v>182880.000</v>
+        <v>181200.000</v>
       </c>
       <c r="C47" s="3">
         <v>1560.000</v>
       </c>
       <c r="D47" s="3">
-        <v>73200.000</v>
+        <v>74880.000</v>
       </c>
       <c r="E47" s="3">
         <v>0.000</v>
@@ -1800,13 +1800,13 @@
         <v>257640.000</v>
       </c>
       <c r="G47" s="4">
-        <v>1.383330</v>
+        <v>1.370690</v>
       </c>
       <c r="H47" s="4">
         <v>0.011740</v>
       </c>
       <c r="I47" s="4">
-        <v>0.548860</v>
+        <v>0.561280</v>
       </c>
       <c r="J47" s="4">
         <v>0.000000</v>
@@ -25095,34 +25095,34 @@
         <v>46284</v>
       </c>
       <c r="B713" s="3">
-        <v>302960.000</v>
+        <v>327320.000</v>
       </c>
       <c r="C713" s="3">
         <v>0.000</v>
       </c>
       <c r="D713" s="3">
-        <v>9800.000</v>
+        <v>17640.000</v>
       </c>
       <c r="E713" s="3">
         <v>1960.000</v>
       </c>
       <c r="F713" s="3">
-        <v>314720.000</v>
+        <v>346920.000</v>
       </c>
       <c r="G713" s="4">
-        <v>2.356260</v>
+        <v>2.545950</v>
       </c>
       <c r="H713" s="4">
         <v>0.000000</v>
       </c>
       <c r="I713" s="4">
-        <v>0.075200</v>
+        <v>0.135440</v>
       </c>
       <c r="J713" s="4">
         <v>0.014830</v>
       </c>
       <c r="K713" s="3">
-        <v>2.446</v>
+        <v>2.696</v>
       </c>
     </row>
   </sheetData>
